--- a/assets/docs/lop1/Giao duc the chat - Lop 1.xlsx
+++ b/assets/docs/lop1/Giao duc the chat - Lop 1.xlsx
@@ -542,7 +542,7 @@
       <c r="D4" s="4" t="inlineStr"/>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: Đội hình đội ngũ — Bài 1: Tư thế đứng nghiêm, đứng nghỉ (Tiết 1)</t>
+          <t>Chủ đề 1: Đội hình đội ngũ — Bài 1: Các tư thế đứng nghiêm, đứng nghỉ (Tiết 1)</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -577,7 +577,7 @@
       <c r="D5" s="4" t="inlineStr"/>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: Đội hình đội ngũ — Bài 1: Tư thế đứng nghiêm, đứng nghỉ (Tiết 2)</t>
+          <t>Chủ đề 1: Đội hình đội ngũ — Bài 1: Các tư thế đứng nghiêm, đứng nghỉ (Tiết 2)</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       <c r="D6" s="4" t="inlineStr"/>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: Đội hình đội ngũ — Bài 1: Tư thế đứng nghiêm, đứng nghỉ (Tiết 3)</t>
+          <t>Chủ đề 1: Đội hình đội ngũ — Bài 1: Các tư thế đứng nghiêm, đứng nghỉ (Tiết 3)</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
